--- a/increase_decrease_mail/increasedecrease(mailtemplate).xlsx
+++ b/increase_decrease_mail/increasedecrease(mailtemplate).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UTHIHI\PycharmProjects\MoamProject\increase_decrease_mail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA1A816-1A83-4286-90FE-7C497B28DEEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B804993F-3B30-4072-87B1-289C7986976B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E2B4C858-E66C-4964-BCD1-67C4BAF22D97}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
   <si>
     <t>Dear VL Treasury,</t>
   </si>
@@ -102,9 +102,6 @@
   </si>
   <si>
     <t>ISIN:</t>
-  </si>
-  <si>
-    <t>NLVLK0009214</t>
   </si>
   <si>
     <t>SWAP ACCRUAD</t>
@@ -335,7 +332,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -393,11 +390,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -775,11 +775,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="E1" s="29" t="str">
+      <c r="E1" s="31" t="str">
         <f>IF(INCREASE\DECREASE="Increase","SPControl: NEW MTN - Opbouwen NOTE/Swap", "SPControl: NEW MTN - Afbouwen NOTE/Swap" )</f>
         <v>SPControl: NEW MTN - Opbouwen NOTE/Swap</v>
       </c>
-      <c r="F1" s="29"/>
+      <c r="F1" s="31"/>
     </row>
     <row r="2" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
@@ -811,11 +811,11 @@
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="29" t="str">
+      <c r="B5" s="31" t="str">
         <f>IF(INCREASE\DECREASE="Increase","We would like to Increase our holdings in the below Note And Swap", "We would like to Decrease our holdings in the below Note and Swap" )</f>
         <v>We would like to Increase our holdings in the below Note And Swap</v>
       </c>
-      <c r="C5" s="29"/>
+      <c r="C5" s="31"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="10"/>
@@ -847,8 +847,8 @@
       </c>
       <c r="K8" s="17"/>
     </row>
-    <row r="9" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="13" t="s">
+    <row r="9" spans="2:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="30" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="17" t="s">
@@ -869,14 +869,12 @@
       <c r="B10" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="17" t="s">
-        <v>15</v>
-      </c>
+      <c r="C10" s="17"/>
       <c r="D10" s="15" t="s">
         <v>9</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J10" s="21">
         <f>(J9/100)*Size</f>
@@ -886,9 +884,9 @@
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="30">
+        <v>16</v>
+      </c>
+      <c r="C11" s="29">
         <v>230000</v>
       </c>
       <c r="D11" s="18" t="s">
@@ -898,7 +896,7 @@
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" s="13" t="str">
         <f ca="1">INDIRECT(C7)</f>
@@ -911,7 +909,7 @@
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" s="22">
         <f>J10</f>
@@ -927,11 +925,11 @@
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E15" s="17">
         <v>0.86350000000000005</v>
@@ -939,12 +937,12 @@
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.25">
@@ -955,7 +953,7 @@
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" s="25">
         <f>Size</f>
@@ -965,12 +963,12 @@
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C21" s="26" t="str">
         <f>IF(Agent="Deutsche Bank", "Please Sign Mark Up Letter", "for your information only")</f>
